--- a/output/roomself_excel/9656.xlsx
+++ b/output/roomself_excel/9656.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>116800</v>
+        <v>95418</v>
       </c>
       <c r="D2" t="n">
-        <v>2768</v>
+        <v>2484</v>
       </c>
       <c r="E2" t="n">
-        <v>624</v>
+        <v>374</v>
       </c>
       <c r="F2" t="n">
-        <v>327</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>134602</v>
+        <v>261378</v>
       </c>
       <c r="D3" t="n">
-        <v>2948</v>
+        <v>4208</v>
       </c>
       <c r="E3" t="n">
-        <v>828</v>
+        <v>696</v>
       </c>
       <c r="F3" t="n">
-        <v>676</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>402934</v>
+        <v>116800</v>
       </c>
       <c r="D4" t="n">
-        <v>8760</v>
+        <v>2768</v>
       </c>
       <c r="E4" t="n">
-        <v>1064</v>
+        <v>436</v>
       </c>
       <c r="F4" t="n">
-        <v>696</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>39961</v>
+        <v>134602</v>
       </c>
       <c r="D5" t="n">
-        <v>1624</v>
+        <v>2948</v>
       </c>
       <c r="E5" t="n">
-        <v>256</v>
+        <v>334</v>
       </c>
       <c r="F5" t="n">
-        <v>217</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33089</v>
+        <v>79453</v>
       </c>
       <c r="D6" t="n">
-        <v>1464</v>
+        <v>2296</v>
       </c>
       <c r="E6" t="n">
-        <v>163</v>
+        <v>233</v>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51359</v>
+        <v>33089</v>
       </c>
       <c r="D7" t="n">
-        <v>1824</v>
+        <v>1464</v>
       </c>
       <c r="E7" t="n">
-        <v>281</v>
+        <v>163</v>
       </c>
       <c r="F7" t="n">
-        <v>244</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>79648</v>
+        <v>21004</v>
       </c>
       <c r="D8" t="n">
-        <v>2704</v>
+        <v>1184</v>
       </c>
       <c r="E8" t="n">
-        <v>550</v>
+        <v>87</v>
       </c>
       <c r="F8" t="n">
-        <v>180</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11931</v>
+        <v>79648</v>
       </c>
       <c r="D9" t="n">
-        <v>880</v>
+        <v>2704</v>
       </c>
       <c r="E9" t="n">
-        <v>123</v>
+        <v>550</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>214551</v>
+        <v>16377</v>
       </c>
       <c r="D10" t="n">
-        <v>4604</v>
+        <v>1048</v>
       </c>
       <c r="E10" t="n">
-        <v>1057</v>
+        <v>172</v>
       </c>
       <c r="F10" t="n">
-        <v>497</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14000</v>
+        <v>44359</v>
       </c>
       <c r="D11" t="n">
-        <v>960</v>
+        <v>1732</v>
       </c>
       <c r="E11" t="n">
-        <v>553</v>
+        <v>251</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16377</v>
+        <v>39961</v>
       </c>
       <c r="D12" t="n">
-        <v>1048</v>
+        <v>1624</v>
       </c>
       <c r="E12" t="n">
-        <v>172</v>
+        <v>256</v>
       </c>
       <c r="F12" t="n">
-        <v>127</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>119739</v>
+        <v>51359</v>
       </c>
       <c r="D13" t="n">
-        <v>5192</v>
+        <v>1824</v>
       </c>
       <c r="E13" t="n">
-        <v>508</v>
+        <v>281</v>
       </c>
       <c r="F13" t="n">
-        <v>424</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>79453</v>
+        <v>11931</v>
       </c>
       <c r="D14" t="n">
-        <v>2296</v>
+        <v>880</v>
       </c>
       <c r="E14" t="n">
-        <v>233</v>
+        <v>123</v>
       </c>
       <c r="F14" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>95418</v>
+        <v>214551</v>
       </c>
       <c r="D15" t="n">
-        <v>2484</v>
+        <v>4604</v>
       </c>
       <c r="E15" t="n">
-        <v>614</v>
+        <v>497</v>
       </c>
       <c r="F15" t="n">
-        <v>299</v>
+        <v>421</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>34662</v>
+        <v>14000</v>
       </c>
       <c r="D16" t="n">
-        <v>1508</v>
+        <v>960</v>
       </c>
       <c r="E16" t="n">
-        <v>276</v>
+        <v>140</v>
       </c>
       <c r="F16" t="n">
-        <v>159</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21004</v>
+        <v>141556</v>
       </c>
       <c r="D17" t="n">
-        <v>1184</v>
+        <v>5488</v>
       </c>
       <c r="E17" t="n">
-        <v>272</v>
+        <v>625</v>
       </c>
       <c r="F17" t="n">
-        <v>118</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>44359</v>
+        <v>119739</v>
       </c>
       <c r="D18" t="n">
-        <v>1732</v>
+        <v>5192</v>
       </c>
       <c r="E18" t="n">
-        <v>251</v>
+        <v>458</v>
       </c>
       <c r="F18" t="n">
-        <v>245</v>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>34662</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1508</v>
+      </c>
+      <c r="E19" t="n">
+        <v>158</v>
+      </c>
+      <c r="F19" t="n">
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/9656.xlsx
+++ b/output/roomself_excel/9656.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,12 +525,34 @@
       <c r="D2" t="n">
         <v>2484</v>
       </c>
-      <c r="E2" t="n">
-        <v>374</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>299</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>271</v>
+      </c>
+      <c r="J2" t="n">
+        <v>32</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +569,42 @@
       <c r="D3" t="n">
         <v>4208</v>
       </c>
-      <c r="E3" t="n">
-        <v>696</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>439</v>
-      </c>
+        <v>648</v>
+      </c>
+      <c r="G3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>404</v>
+      </c>
+      <c r="J3" t="n">
+        <v>28</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>403</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +621,34 @@
       <c r="D4" t="n">
         <v>2768</v>
       </c>
-      <c r="E4" t="n">
-        <v>436</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>327</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="G4" t="n">
+        <v>36</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>400</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +665,34 @@
       <c r="D5" t="n">
         <v>2948</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>334</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>36</v>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>403</v>
+      </c>
+      <c r="J5" t="n">
+        <v>35</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +709,34 @@
       <c r="D6" t="n">
         <v>2296</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>341</v>
+      </c>
+      <c r="G6" t="n">
+        <v>35</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>233</v>
       </c>
-      <c r="F6" t="n">
+      <c r="J6" t="n">
         <v>35</v>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +753,26 @@
       <c r="D7" t="n">
         <v>1464</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>163</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>41</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +789,26 @@
       <c r="D8" t="n">
         <v>1184</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>87</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>32</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +825,34 @@
       <c r="D9" t="n">
         <v>2704</v>
       </c>
-      <c r="E9" t="n">
-        <v>550</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>180</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="G9" t="n">
+        <v>28</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>152</v>
+      </c>
+      <c r="J9" t="n">
+        <v>26</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +869,26 @@
       <c r="D10" t="n">
         <v>1048</v>
       </c>
-      <c r="E10" t="n">
-        <v>172</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>127</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="G10" t="n">
+        <v>24</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +905,42 @@
       <c r="D11" t="n">
         <v>1732</v>
       </c>
-      <c r="E11" t="n">
-        <v>251</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>245</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="G11" t="n">
+        <v>26</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>203</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>209</v>
+      </c>
+      <c r="M11" t="n">
+        <v>26</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +957,34 @@
       <c r="D12" t="n">
         <v>1624</v>
       </c>
-      <c r="E12" t="n">
-        <v>256</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>217</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="G12" t="n">
+        <v>41</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>215</v>
+      </c>
+      <c r="J12" t="n">
+        <v>26</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +1001,34 @@
       <c r="D13" t="n">
         <v>1824</v>
       </c>
-      <c r="E13" t="n">
-        <v>281</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>244</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="G13" t="n">
+        <v>41</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>203</v>
+      </c>
+      <c r="J13" t="n">
+        <v>28</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +1045,26 @@
       <c r="D14" t="n">
         <v>880</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>123</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>28</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1081,34 @@
       <c r="D15" t="n">
         <v>4604</v>
       </c>
-      <c r="E15" t="n">
-        <v>497</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>421</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="G15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>246</v>
+      </c>
+      <c r="J15" t="n">
+        <v>26</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1125,26 @@
       <c r="D16" t="n">
         <v>960</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>140</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>16</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,11 +1161,49 @@
       <c r="D17" t="n">
         <v>5488</v>
       </c>
-      <c r="E17" t="n">
-        <v>625</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>285</v>
+        <v>593</v>
+      </c>
+      <c r="G17" t="n">
+        <v>28</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>96</v>
+      </c>
+      <c r="J17" t="n">
+        <v>44</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>97</v>
+      </c>
+      <c r="M17" t="n">
+        <v>37</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>220</v>
+      </c>
+      <c r="P17" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -827,12 +1221,42 @@
       <c r="D18" t="n">
         <v>5192</v>
       </c>
-      <c r="E18" t="n">
-        <v>458</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>255</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="G18" t="n">
+        <v>24</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>200</v>
+      </c>
+      <c r="J18" t="n">
+        <v>18</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>213</v>
+      </c>
+      <c r="M18" t="n">
+        <v>32</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1273,26 @@
       <c r="D19" t="n">
         <v>1508</v>
       </c>
-      <c r="E19" t="n">
-        <v>158</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>139</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="G19" t="n">
+        <v>35</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
